--- a/quizzes/038_international_women_039_s_day_quiz--quizzes.xlsx
+++ b/quizzes/038_international_women_039_s_day_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro_page</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>International Women's Day Quiz</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Welcome to the International Women's Day Quiz!</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,12 +547,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>q1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_iwd</t>
+          <t>What is International Women's Day (IWD)?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +570,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question1_answer</t>
+          <t>q1_answer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iwd_awareness</t>
+          <t>International Women's Day is a global event</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +593,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question2</t>
+          <t>q2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iwd_purpose</t>
+          <t>What is the purpose of IWD?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +616,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question2_answer</t>
+          <t>q2_answer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iwd_purpose_answer</t>
+          <t>International Women's Day promotes women's empowerment</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +639,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question3</t>
+          <t>q3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iwd_history</t>
+          <t>How do people usually celebrate IWD?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +657,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question3_answer</t>
+          <t>q3_answer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iwd_history_answer</t>
+          <t>With parties and gifts</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +685,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question4</t>
+          <t>q4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iwd_mission</t>
+          <t>What is the main mission of IWD?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +708,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question4_answer</t>
+          <t>q4_answer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iwd_mission_answer</t>
+          <t>Supporting women's rights</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +731,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question5</t>
+          <t>q5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iwd_awareness</t>
+          <t>When is International Women's Day celebrated?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +754,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question5_answer</t>
+          <t>q5_answer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iwd_awareness_answer</t>
+          <t>March 8th</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +772,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question6</t>
+          <t>q6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iwd_awareness_2</t>
+          <t>What is the awareness of IWD?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +795,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question6_answer</t>
+          <t>q7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iwd_awareness_2_answer</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +823,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question7</t>
+          <t>q8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iwd_mission</t>
+          <t>How do you celebrate IWD?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question7_answer</t>
+          <t>q9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>iwd_mission_answer</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +864,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question8</t>
+          <t>q10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>iwd_purpose</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question9</t>
+          <t>q11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>iwd_awareness</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question9_answer</t>
+          <t>q12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>iwd_awareness_answer</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +933,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>question10</t>
+          <t>question13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>iwd_awareness_2</t>
+          <t>Awareness of IWD?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,136 +956,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>question10_answer</t>
+          <t>question13_answer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>iwd_awareness_2_answer</t>
+          <t>Understanding the significance of IWD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>iwd_mission</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question11_answer</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>iwd_mission_answer</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question12</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>iwd_purpose</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question12_answer</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>iwd_purpose_answer</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question13</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>iwd_purpose_answer_2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +987,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,459 +1015,408 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question1_answer_choices</t>
+          <t>q1_answer_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'option_a'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'option_a'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question1_answer_choices</t>
+          <t>q1_answer_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'option_b'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'option_b'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question1_answer_choices</t>
+          <t>q1_answer_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'option_c'}</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'option_c'}</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question2_answer_choices</t>
+          <t>q2_answer_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'option_a'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'option_a'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question2_answer_choices</t>
+          <t>q2_answer_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'option_b'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'option_b'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question2_answer_choices</t>
+          <t>q2_answer_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'option_c'}</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'option_c'}</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question3_answer_choices</t>
+          <t>q3_answer_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'option_a'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'option_a'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question3_answer_choices</t>
+          <t>q3_answer_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'option_b'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'option_b'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question3_answer_choices</t>
+          <t>q3_answer_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'option_c'}</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'option_c'}</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question4_answer_choices</t>
+          <t>q4_answer_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'option_a'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'option_a'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question4_answer_choices</t>
+          <t>q4_answer_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'option_b'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'option_b'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question4_answer_choices</t>
+          <t>q4_answer_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'option_c'}</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'option_c'}</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question7_answer_choices</t>
+          <t>q7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'option_a'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'option_a'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question7_answer_choices</t>
+          <t>q7_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'option_b'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'option_b'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question7_answer_choices</t>
+          <t>q7_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'option_c'}</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'option_c'}</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question8_choices</t>
+          <t>q9_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'option_a'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'option_a'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question8_choices</t>
+          <t>q9_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'option_b'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'option_b'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question8_choices</t>
+          <t>q9_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'option_c'}</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'option_c'}</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question9_answer_choices</t>
+          <t>q12_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'option_a'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'option_a'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question9_answer_choices</t>
+          <t>q12_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'option_b'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'option_b'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question9_answer_choices</t>
+          <t>q12_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'option_c'}</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'option_c'}</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question12_answer_choices</t>
+          <t>question13_answer_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'option_a'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'option_a'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question12_answer_choices</t>
+          <t>question13_answer_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'option_b'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'option_b'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question12_answer_choices</t>
+          <t>question13_answer_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'option_c'}</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'option_c'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>question13_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'option_a'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'option_a'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>question13_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'option_b'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'option_b'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>question13_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'option_c'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'option_c'}</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
